--- a/data/stocks_20260324_100252.xlsx
+++ b/data/stocks_20260324_100252.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,10 +519,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>000858</t>
-        </is>
+      <c r="A2" t="n">
+        <v>858</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -587,10 +585,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="A3" t="n">
+        <v>300750</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -655,10 +651,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>600030</t>
-        </is>
+      <c r="A4" t="n">
+        <v>600030</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -723,10 +717,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>600118</t>
-        </is>
+      <c r="A5" t="n">
+        <v>600118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -791,10 +783,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="A6" t="n">
+        <v>300308</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -859,10 +849,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>601398</t>
-        </is>
+      <c r="A7" t="n">
+        <v>601398</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -927,10 +915,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>601919</t>
-        </is>
+      <c r="A8" t="n">
+        <v>601919</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -995,10 +981,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>002261</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2261</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1063,10 +1047,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="A10" t="n">
+        <v>688041</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1131,10 +1113,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="A11" t="n">
+        <v>300502</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1199,10 +1179,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="A12" t="n">
+        <v>300394</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1267,10 +1245,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="A13" t="n">
+        <v>988</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1335,10 +1311,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>603986</t>
-        </is>
+      <c r="A14" t="n">
+        <v>603986</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1403,10 +1377,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>688525</t>
-        </is>
+      <c r="A15" t="n">
+        <v>688525</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1471,10 +1443,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>300042</t>
-        </is>
+      <c r="A16" t="n">
+        <v>300042</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1539,10 +1509,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>300302</t>
-        </is>
+      <c r="A17" t="n">
+        <v>300302</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1607,10 +1575,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>000020</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1675,10 +1641,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>603881</t>
-        </is>
+      <c r="A19" t="n">
+        <v>603881</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1743,10 +1707,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>300017</t>
-        </is>
+      <c r="A20" t="n">
+        <v>300017</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1811,10 +1773,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>300418</t>
-        </is>
+      <c r="A21" t="n">
+        <v>300418</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1879,10 +1839,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>002230</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2230</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1947,10 +1905,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>300058</t>
-        </is>
+      <c r="A23" t="n">
+        <v>300058</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2015,10 +1971,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>300496</t>
-        </is>
+      <c r="A24" t="n">
+        <v>300496</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2083,10 +2037,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
+      <c r="A25" t="n">
+        <v>547</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2151,10 +2103,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>002202</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2202</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2219,10 +2169,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
+      <c r="A27" t="n">
+        <v>301128</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2281,6 +2229,774 @@
         <v>12.4</v>
       </c>
       <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>601899</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="F28" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.747</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.142</v>
+      </c>
+      <c r="J28" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="K28" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45726.45</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31672.99</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P28" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>600219</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>南山铝业</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.271</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20093.49</v>
+      </c>
+      <c r="N29" t="n">
+        <v>31051.78</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>601939</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>建设银行</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J30" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>82.91</v>
+      </c>
+      <c r="L30" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11089.72</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10791.49</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>600048</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>保利发展</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9708.51</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14056.98</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>600941</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>中国移动</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="F32" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="G32" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="J32" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K32" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1014.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1144.22</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P32" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>93.37</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2352</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>顺丰控股</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E33" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="G33" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.504</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.369</v>
+      </c>
+      <c r="J33" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1530.36</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2618.46</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P33" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>603803</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>瑞斯康达</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J34" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="L34" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>14058.22</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5675.64</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P34" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2624</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>完美世界</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.526</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.092</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="K35" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4451.95</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6248.82</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P35" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="R35" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2558</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>巨人网络</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34</v>
+      </c>
+      <c r="G36" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.634</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2.531</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2884.64</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4524.12</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P36" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>601088</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国神华</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="E37" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="G37" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="J37" t="n">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="K37" t="n">
+        <v>75.27</v>
+      </c>
+      <c r="L37" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4656.28</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4880.38</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P37" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="R37" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>600963</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>岳阳林纸</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.238</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4000.37</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6039.77</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>601877</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>正泰电器</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="F39" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="J39" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5399.86</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5858.36</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P39" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="R39" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>

--- a/data/stocks_20260324_100252.xlsx
+++ b/data/stocks_20260324_100252.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,63 +1048,63 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213.27</v>
+        <v>468</v>
       </c>
       <c r="D10" t="n">
-        <v>3.01</v>
+        <v>1.64</v>
       </c>
       <c r="E10" t="n">
-        <v>218.15</v>
+        <v>455.36</v>
       </c>
       <c r="F10" t="n">
-        <v>227.36</v>
+        <v>424.54</v>
       </c>
       <c r="G10" t="n">
-        <v>237.04</v>
+        <v>404.51</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.018</v>
+        <v>18.827</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.494999999999999</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>12.87</v>
+        <v>79.03</v>
       </c>
       <c r="K10" t="n">
-        <v>15.47</v>
+        <v>74.83</v>
       </c>
       <c r="L10" t="n">
-        <v>7.67</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>22.1</v>
+        <v>40.69</v>
       </c>
       <c r="N10" t="n">
-        <v>21.1</v>
+        <v>46.27</v>
       </c>
       <c r="O10" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="P10" t="n">
-        <v>210.69</v>
+        <v>459</v>
       </c>
       <c r="Q10" t="n">
-        <v>213.98</v>
+        <v>468.33</v>
       </c>
       <c r="R10" t="n">
-        <v>202.98</v>
+        <v>438</v>
       </c>
       <c r="S10" t="n">
-        <v>0.95</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1114,63 +1114,63 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>468</v>
+        <v>298.71</v>
       </c>
       <c r="D11" t="n">
-        <v>1.64</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>455.36</v>
+        <v>304.1</v>
       </c>
       <c r="F11" t="n">
-        <v>424.54</v>
+        <v>310.17</v>
       </c>
       <c r="G11" t="n">
-        <v>404.51</v>
+        <v>324.96</v>
       </c>
       <c r="H11" t="n">
-        <v>18.827</v>
+        <v>6.163</v>
       </c>
       <c r="I11" t="n">
-        <v>9.747999999999999</v>
+        <v>13.65</v>
       </c>
       <c r="J11" t="n">
-        <v>79.03</v>
+        <v>37.48</v>
       </c>
       <c r="K11" t="n">
-        <v>74.83</v>
+        <v>37.52</v>
       </c>
       <c r="L11" t="n">
-        <v>87.43000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="M11" t="n">
-        <v>40.69</v>
+        <v>30.85</v>
       </c>
       <c r="N11" t="n">
-        <v>46.27</v>
+        <v>36.84</v>
       </c>
       <c r="O11" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="P11" t="n">
-        <v>459</v>
+        <v>298.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>468.33</v>
+        <v>308.88</v>
       </c>
       <c r="R11" t="n">
-        <v>438</v>
+        <v>290.5</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1180,63 +1180,63 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>298.71</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.18</v>
       </c>
       <c r="E12" t="n">
-        <v>304.1</v>
+        <v>115.24</v>
       </c>
       <c r="F12" t="n">
-        <v>310.17</v>
+        <v>118.6</v>
       </c>
       <c r="G12" t="n">
-        <v>324.96</v>
+        <v>110.32</v>
       </c>
       <c r="H12" t="n">
-        <v>6.163</v>
+        <v>8.025</v>
       </c>
       <c r="I12" t="n">
-        <v>13.65</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>37.48</v>
+        <v>22.6</v>
       </c>
       <c r="K12" t="n">
-        <v>37.52</v>
+        <v>34.34</v>
       </c>
       <c r="L12" t="n">
-        <v>37.4</v>
+        <v>-0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>30.85</v>
+        <v>116.87</v>
       </c>
       <c r="N12" t="n">
-        <v>36.84</v>
+        <v>125.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="P12" t="n">
-        <v>298.49</v>
+        <v>113.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>308.88</v>
+        <v>115.15</v>
       </c>
       <c r="R12" t="n">
-        <v>290.5</v>
+        <v>105.55</v>
       </c>
       <c r="S12" t="n">
-        <v>3.98</v>
+        <v>11.63</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1246,63 +1246,63 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>273.71</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.18</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>115.24</v>
+        <v>290.44</v>
       </c>
       <c r="F13" t="n">
-        <v>118.6</v>
+        <v>288.9</v>
       </c>
       <c r="G13" t="n">
-        <v>110.32</v>
+        <v>289.21</v>
       </c>
       <c r="H13" t="n">
-        <v>8.025</v>
+        <v>-2.462</v>
       </c>
       <c r="I13" t="n">
-        <v>9.390000000000001</v>
+        <v>-1.578</v>
       </c>
       <c r="J13" t="n">
-        <v>22.6</v>
+        <v>39.98</v>
       </c>
       <c r="K13" t="n">
-        <v>34.34</v>
+        <v>51.23</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.89</v>
+        <v>17.46</v>
       </c>
       <c r="M13" t="n">
-        <v>116.87</v>
+        <v>33.69</v>
       </c>
       <c r="N13" t="n">
-        <v>125.2</v>
+        <v>28.48</v>
       </c>
       <c r="O13" t="n">
-        <v>0.93</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>113.54</v>
+        <v>277.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>115.15</v>
+        <v>278</v>
       </c>
       <c r="R13" t="n">
-        <v>105.55</v>
+        <v>256.88</v>
       </c>
       <c r="S13" t="n">
-        <v>11.63</v>
+        <v>5.04</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1312,63 +1312,63 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>273.71</v>
+        <v>47.59</v>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>-1.08</v>
       </c>
       <c r="E14" t="n">
-        <v>290.44</v>
+        <v>53.03</v>
       </c>
       <c r="F14" t="n">
-        <v>288.9</v>
+        <v>47.72</v>
       </c>
       <c r="G14" t="n">
-        <v>289.21</v>
+        <v>41.83</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.462</v>
+        <v>4.522</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.578</v>
+        <v>3.64</v>
       </c>
       <c r="J14" t="n">
-        <v>39.98</v>
+        <v>59.05</v>
       </c>
       <c r="K14" t="n">
-        <v>51.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>17.46</v>
+        <v>35.17</v>
       </c>
       <c r="M14" t="n">
-        <v>33.69</v>
+        <v>35.57</v>
       </c>
       <c r="N14" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>277.99</v>
+        <v>48.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>278</v>
+        <v>48.2</v>
       </c>
       <c r="R14" t="n">
-        <v>256.88</v>
+        <v>45.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5.04</v>
+        <v>17.75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1378,63 +1378,63 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>231.5</v>
+        <v>22.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2.89</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>239.33</v>
+        <v>24.19</v>
       </c>
       <c r="F15" t="n">
-        <v>229.67</v>
+        <v>22.2</v>
       </c>
       <c r="G15" t="n">
-        <v>205.62</v>
+        <v>20.52</v>
       </c>
       <c r="H15" t="n">
-        <v>16.165</v>
+        <v>1.001</v>
       </c>
       <c r="I15" t="n">
-        <v>13.671</v>
+        <v>0.546</v>
       </c>
       <c r="J15" t="n">
-        <v>61.26</v>
+        <v>53.8</v>
       </c>
       <c r="K15" t="n">
-        <v>72.05</v>
+        <v>66.81</v>
       </c>
       <c r="L15" t="n">
-        <v>39.69</v>
+        <v>27.77</v>
       </c>
       <c r="M15" t="n">
-        <v>44.6</v>
+        <v>49.98</v>
       </c>
       <c r="N15" t="n">
-        <v>39.84</v>
+        <v>36.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>228.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>231.78</v>
+        <v>22.94</v>
       </c>
       <c r="R15" t="n">
-        <v>212.97</v>
+        <v>21.62</v>
       </c>
       <c r="S15" t="n">
-        <v>9.550000000000001</v>
+        <v>13.55</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1444,63 +1444,63 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47.59</v>
+        <v>18.95</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.08</v>
+        <v>-9.76</v>
       </c>
       <c r="E16" t="n">
-        <v>53.03</v>
+        <v>20.75</v>
       </c>
       <c r="F16" t="n">
-        <v>47.72</v>
+        <v>18.1</v>
       </c>
       <c r="G16" t="n">
-        <v>41.83</v>
+        <v>16.35</v>
       </c>
       <c r="H16" t="n">
-        <v>4.522</v>
+        <v>1.451</v>
       </c>
       <c r="I16" t="n">
-        <v>3.64</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>59.05</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>70.98999999999999</v>
+        <v>78.33</v>
       </c>
       <c r="L16" t="n">
-        <v>35.17</v>
+        <v>48.95</v>
       </c>
       <c r="M16" t="n">
-        <v>35.57</v>
+        <v>41.19</v>
       </c>
       <c r="N16" t="n">
-        <v>28.63</v>
+        <v>7.72</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>5.34</v>
       </c>
       <c r="P16" t="n">
-        <v>48.13</v>
+        <v>20.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.2</v>
+        <v>20.58</v>
       </c>
       <c r="R16" t="n">
-        <v>45.2</v>
+        <v>18.9</v>
       </c>
       <c r="S16" t="n">
-        <v>17.75</v>
+        <v>22.74</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1510,63 +1510,63 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>36.37</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>3.03</v>
       </c>
       <c r="E17" t="n">
-        <v>24.19</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="n">
-        <v>22.2</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>20.52</v>
+        <v>37.58</v>
       </c>
       <c r="H17" t="n">
-        <v>1.001</v>
+        <v>-0.347</v>
       </c>
       <c r="I17" t="n">
-        <v>0.546</v>
+        <v>-0.137</v>
       </c>
       <c r="J17" t="n">
-        <v>53.8</v>
+        <v>38.36</v>
       </c>
       <c r="K17" t="n">
-        <v>66.81</v>
+        <v>42.55</v>
       </c>
       <c r="L17" t="n">
-        <v>27.77</v>
+        <v>29.98</v>
       </c>
       <c r="M17" t="n">
-        <v>49.98</v>
+        <v>60.55</v>
       </c>
       <c r="N17" t="n">
-        <v>36.8</v>
+        <v>63.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>0.95</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>36.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.94</v>
+        <v>36.67</v>
       </c>
       <c r="R17" t="n">
-        <v>21.62</v>
+        <v>34.66</v>
       </c>
       <c r="S17" t="n">
-        <v>13.55</v>
+        <v>8.43</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1576,63 +1576,63 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18.95</v>
+        <v>16.92</v>
       </c>
       <c r="D18" t="n">
-        <v>-9.76</v>
+        <v>1.38</v>
       </c>
       <c r="E18" t="n">
-        <v>20.75</v>
+        <v>17.65</v>
       </c>
       <c r="F18" t="n">
-        <v>18.1</v>
+        <v>17.88</v>
       </c>
       <c r="G18" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>154.19</v>
+      </c>
+      <c r="N18" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P18" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="R18" t="n">
         <v>16.35</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.451</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>68.54000000000001</v>
-      </c>
-      <c r="K18" t="n">
-        <v>78.33</v>
-      </c>
-      <c r="L18" t="n">
-        <v>48.95</v>
-      </c>
-      <c r="M18" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>20.36</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="R18" t="n">
-        <v>18.9</v>
-      </c>
       <c r="S18" t="n">
-        <v>22.74</v>
+        <v>6.69</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1642,63 +1642,63 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36.37</v>
+        <v>48.35</v>
       </c>
       <c r="D19" t="n">
-        <v>3.03</v>
+        <v>-3.16</v>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>51.38</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>51.35</v>
       </c>
       <c r="G19" t="n">
-        <v>37.58</v>
+        <v>53.49</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.347</v>
+        <v>-1.67</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.137</v>
+        <v>-1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>38.36</v>
+        <v>27.01</v>
       </c>
       <c r="K19" t="n">
-        <v>42.55</v>
+        <v>28.87</v>
       </c>
       <c r="L19" t="n">
-        <v>29.98</v>
+        <v>23.28</v>
       </c>
       <c r="M19" t="n">
-        <v>60.55</v>
+        <v>71.84</v>
       </c>
       <c r="N19" t="n">
-        <v>63.5</v>
+        <v>77.23</v>
       </c>
       <c r="O19" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="P19" t="n">
-        <v>36.01</v>
+        <v>50.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.67</v>
+        <v>50.85</v>
       </c>
       <c r="R19" t="n">
-        <v>34.66</v>
+        <v>46.89</v>
       </c>
       <c r="S19" t="n">
-        <v>8.43</v>
+        <v>5.73</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1708,63 +1708,63 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.92</v>
+        <v>46.83</v>
       </c>
       <c r="D20" t="n">
-        <v>1.38</v>
+        <v>0.82</v>
       </c>
       <c r="E20" t="n">
-        <v>17.65</v>
+        <v>48.86</v>
       </c>
       <c r="F20" t="n">
-        <v>17.88</v>
+        <v>50.51</v>
       </c>
       <c r="G20" t="n">
-        <v>18.54</v>
+        <v>52.14</v>
       </c>
       <c r="H20" t="n">
-        <v>0.017</v>
+        <v>-2.182</v>
       </c>
       <c r="I20" t="n">
-        <v>0.434</v>
+        <v>-1.684</v>
       </c>
       <c r="J20" t="n">
-        <v>16.59</v>
+        <v>10.47</v>
       </c>
       <c r="K20" t="n">
-        <v>21.19</v>
+        <v>13.95</v>
       </c>
       <c r="L20" t="n">
-        <v>7.39</v>
+        <v>3.51</v>
       </c>
       <c r="M20" t="n">
-        <v>154.19</v>
+        <v>38.38</v>
       </c>
       <c r="N20" t="n">
-        <v>345.15</v>
+        <v>41.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="P20" t="n">
-        <v>17.17</v>
+        <v>47.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.17</v>
+        <v>47.28</v>
       </c>
       <c r="R20" t="n">
-        <v>16.35</v>
+        <v>45.74</v>
       </c>
       <c r="S20" t="n">
-        <v>6.69</v>
+        <v>1.75</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1774,63 +1774,63 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48.35</v>
+        <v>13.92</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.16</v>
+        <v>2.2</v>
       </c>
       <c r="E21" t="n">
-        <v>51.38</v>
+        <v>14.5</v>
       </c>
       <c r="F21" t="n">
-        <v>51.35</v>
+        <v>14.99</v>
       </c>
       <c r="G21" t="n">
-        <v>53.49</v>
+        <v>16.07</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.67</v>
+        <v>-1.346</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3</v>
+        <v>-1.222</v>
       </c>
       <c r="J21" t="n">
-        <v>27.01</v>
+        <v>9.75</v>
       </c>
       <c r="K21" t="n">
-        <v>28.87</v>
+        <v>10.41</v>
       </c>
       <c r="L21" t="n">
-        <v>23.28</v>
+        <v>8.44</v>
       </c>
       <c r="M21" t="n">
-        <v>71.84</v>
+        <v>196.79</v>
       </c>
       <c r="N21" t="n">
-        <v>77.23</v>
+        <v>302.41</v>
       </c>
       <c r="O21" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="P21" t="n">
-        <v>50.76</v>
+        <v>13.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.85</v>
+        <v>14.03</v>
       </c>
       <c r="R21" t="n">
-        <v>46.89</v>
+        <v>13.5</v>
       </c>
       <c r="S21" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1840,63 +1840,63 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.83</v>
+        <v>60.68</v>
       </c>
       <c r="D22" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="E22" t="n">
-        <v>48.86</v>
+        <v>63.12</v>
       </c>
       <c r="F22" t="n">
-        <v>50.51</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>52.14</v>
+        <v>67.33</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.182</v>
+        <v>-3.035</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.684</v>
+        <v>-2.511</v>
       </c>
       <c r="J22" t="n">
-        <v>10.47</v>
+        <v>10.08</v>
       </c>
       <c r="K22" t="n">
-        <v>13.95</v>
+        <v>14.28</v>
       </c>
       <c r="L22" t="n">
-        <v>3.51</v>
+        <v>1.68</v>
       </c>
       <c r="M22" t="n">
-        <v>38.38</v>
+        <v>11.49</v>
       </c>
       <c r="N22" t="n">
-        <v>41.35</v>
+        <v>14.16</v>
       </c>
       <c r="O22" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>47.16</v>
+        <v>61.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>47.28</v>
+        <v>61.98</v>
       </c>
       <c r="R22" t="n">
-        <v>45.74</v>
+        <v>59.16</v>
       </c>
       <c r="S22" t="n">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -1906,63 +1906,63 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.92</v>
+        <v>26.93</v>
       </c>
       <c r="D23" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="E23" t="n">
-        <v>14.5</v>
+        <v>28.6</v>
       </c>
       <c r="F23" t="n">
-        <v>14.99</v>
+        <v>30.12</v>
       </c>
       <c r="G23" t="n">
-        <v>16.07</v>
+        <v>30.67</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.346</v>
+        <v>-0.451</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.222</v>
+        <v>0.183</v>
       </c>
       <c r="J23" t="n">
-        <v>9.75</v>
+        <v>19.9</v>
       </c>
       <c r="K23" t="n">
-        <v>10.41</v>
+        <v>28.69</v>
       </c>
       <c r="L23" t="n">
-        <v>8.44</v>
+        <v>2.33</v>
       </c>
       <c r="M23" t="n">
-        <v>196.79</v>
+        <v>225.66</v>
       </c>
       <c r="N23" t="n">
-        <v>302.41</v>
+        <v>257.34</v>
       </c>
       <c r="O23" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="P23" t="n">
-        <v>13.96</v>
+        <v>26.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>14.03</v>
+        <v>27.29</v>
       </c>
       <c r="R23" t="n">
-        <v>13.5</v>
+        <v>24.83</v>
       </c>
       <c r="S23" t="n">
-        <v>5.65</v>
+        <v>14.2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -1972,63 +1972,63 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60.68</v>
+        <v>27.58</v>
       </c>
       <c r="D24" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="E24" t="n">
-        <v>63.12</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>65.40000000000001</v>
+        <v>29.75</v>
       </c>
       <c r="G24" t="n">
-        <v>67.33</v>
+        <v>28.82</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.035</v>
+        <v>0.314</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.511</v>
+        <v>0.496</v>
       </c>
       <c r="J24" t="n">
-        <v>10.08</v>
+        <v>22.38</v>
       </c>
       <c r="K24" t="n">
-        <v>14.28</v>
+        <v>38.07</v>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>-8.99</v>
       </c>
       <c r="M24" t="n">
-        <v>11.49</v>
+        <v>204.46</v>
       </c>
       <c r="N24" t="n">
-        <v>14.16</v>
+        <v>303.39</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="P24" t="n">
-        <v>61.93</v>
+        <v>28.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>61.98</v>
+        <v>28.23</v>
       </c>
       <c r="R24" t="n">
-        <v>59.16</v>
+        <v>27.04</v>
       </c>
       <c r="S24" t="n">
-        <v>3.12</v>
+        <v>6.08</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2038,63 +2038,63 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.93</v>
+        <v>133.92</v>
       </c>
       <c r="D25" t="n">
-        <v>2.43</v>
+        <v>6.33</v>
       </c>
       <c r="E25" t="n">
-        <v>28.6</v>
+        <v>131.55</v>
       </c>
       <c r="F25" t="n">
-        <v>30.12</v>
+        <v>120.38</v>
       </c>
       <c r="G25" t="n">
-        <v>30.67</v>
+        <v>114</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.451</v>
+        <v>5.633</v>
       </c>
       <c r="I25" t="n">
-        <v>0.183</v>
+        <v>2.627</v>
       </c>
       <c r="J25" t="n">
-        <v>19.9</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>28.69</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>2.33</v>
+        <v>78.12</v>
       </c>
       <c r="M25" t="n">
-        <v>225.66</v>
+        <v>10.94</v>
       </c>
       <c r="N25" t="n">
-        <v>257.34</v>
+        <v>6.61</v>
       </c>
       <c r="O25" t="n">
-        <v>0.88</v>
+        <v>1.66</v>
       </c>
       <c r="P25" t="n">
-        <v>26.88</v>
+        <v>126</v>
       </c>
       <c r="Q25" t="n">
-        <v>27.29</v>
+        <v>133.92</v>
       </c>
       <c r="R25" t="n">
-        <v>24.83</v>
+        <v>121.4</v>
       </c>
       <c r="S25" t="n">
-        <v>14.2</v>
+        <v>12.4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2104,64 +2104,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.58</v>
+        <v>32.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.62</v>
+        <v>5.3</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>32.33</v>
       </c>
       <c r="F26" t="n">
-        <v>29.75</v>
+        <v>34.11</v>
       </c>
       <c r="G26" t="n">
-        <v>28.82</v>
+        <v>36.28</v>
       </c>
       <c r="H26" t="n">
-        <v>0.314</v>
+        <v>-1.747</v>
       </c>
       <c r="I26" t="n">
-        <v>0.496</v>
+        <v>-1.142</v>
       </c>
       <c r="J26" t="n">
-        <v>22.38</v>
+        <v>19.54</v>
       </c>
       <c r="K26" t="n">
-        <v>38.07</v>
+        <v>19.2</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.99</v>
+        <v>20.22</v>
       </c>
       <c r="M26" t="n">
-        <v>204.46</v>
+        <v>45726.45</v>
       </c>
       <c r="N26" t="n">
-        <v>303.39</v>
+        <v>31672.99</v>
       </c>
       <c r="O26" t="n">
-        <v>0.67</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>28.08</v>
+        <v>31.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>28.23</v>
+        <v>32.38</v>
       </c>
       <c r="R26" t="n">
-        <v>27.04</v>
-      </c>
-      <c r="S26" t="n">
-        <v>6.08</v>
-      </c>
+        <v>30.91</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -2170,64 +2168,62 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>133.92</v>
+        <v>5.88</v>
       </c>
       <c r="D27" t="n">
-        <v>6.33</v>
+        <v>2.08</v>
       </c>
       <c r="E27" t="n">
-        <v>131.55</v>
+        <v>6.06</v>
       </c>
       <c r="F27" t="n">
-        <v>120.38</v>
+        <v>6.66</v>
       </c>
       <c r="G27" t="n">
-        <v>114</v>
+        <v>7.01</v>
       </c>
       <c r="H27" t="n">
-        <v>5.633</v>
+        <v>-0.271</v>
       </c>
       <c r="I27" t="n">
-        <v>2.627</v>
+        <v>-0.08</v>
       </c>
       <c r="J27" t="n">
-        <v>75.98999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="K27" t="n">
-        <v>74.93000000000001</v>
+        <v>13.13</v>
       </c>
       <c r="L27" t="n">
-        <v>78.12</v>
+        <v>-3.07</v>
       </c>
       <c r="M27" t="n">
-        <v>10.94</v>
+        <v>20093.49</v>
       </c>
       <c r="N27" t="n">
-        <v>6.61</v>
+        <v>31051.78</v>
       </c>
       <c r="O27" t="n">
-        <v>1.66</v>
+        <v>0.65</v>
       </c>
       <c r="P27" t="n">
-        <v>126</v>
+        <v>5.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>133.92</v>
+        <v>5.9</v>
       </c>
       <c r="R27" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>12.4</v>
-      </c>
+        <v>5.68</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -2236,60 +2232,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.2</v>
+        <v>9.32</v>
       </c>
       <c r="D28" t="n">
-        <v>5.3</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
-        <v>32.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>34.11</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>36.28</v>
+        <v>9.02</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.747</v>
+        <v>0.142</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.142</v>
+        <v>0.12</v>
       </c>
       <c r="J28" t="n">
-        <v>19.54</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>19.2</v>
+        <v>82.91</v>
       </c>
       <c r="L28" t="n">
-        <v>20.22</v>
+        <v>70.87</v>
       </c>
       <c r="M28" t="n">
-        <v>45726.45</v>
+        <v>11089.72</v>
       </c>
       <c r="N28" t="n">
-        <v>31672.99</v>
+        <v>10791.49</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="P28" t="n">
-        <v>31.25</v>
+        <v>9.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>32.38</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>30.91</v>
+        <v>9.15</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
@@ -2300,60 +2296,60 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K29" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9708.51</v>
+      </c>
+      <c r="N29" t="n">
+        <v>14056.98</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" t="n">
         <v>5.88</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E29" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.271</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="K29" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-3.07</v>
-      </c>
-      <c r="M29" t="n">
-        <v>20093.49</v>
-      </c>
-      <c r="N29" t="n">
-        <v>31051.78</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="P29" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R29" t="n">
-        <v>5.68</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
@@ -2364,60 +2360,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.32</v>
+        <v>93.88</v>
       </c>
       <c r="D30" t="n">
-        <v>1.75</v>
+        <v>0.65</v>
       </c>
       <c r="E30" t="n">
-        <v>9.289999999999999</v>
+        <v>95.95</v>
       </c>
       <c r="F30" t="n">
-        <v>9.220000000000001</v>
+        <v>96.61</v>
       </c>
       <c r="G30" t="n">
-        <v>9.02</v>
+        <v>95.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.142</v>
+        <v>0.198</v>
       </c>
       <c r="I30" t="n">
-        <v>0.12</v>
+        <v>0.467</v>
       </c>
       <c r="J30" t="n">
-        <v>78.90000000000001</v>
+        <v>35.13</v>
       </c>
       <c r="K30" t="n">
-        <v>82.91</v>
+        <v>56.1</v>
       </c>
       <c r="L30" t="n">
-        <v>70.87</v>
+        <v>-6.81</v>
       </c>
       <c r="M30" t="n">
-        <v>11089.72</v>
+        <v>1014.2</v>
       </c>
       <c r="N30" t="n">
-        <v>10791.49</v>
+        <v>1144.22</v>
       </c>
       <c r="O30" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="P30" t="n">
-        <v>9.16</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.369999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="R30" t="n">
-        <v>9.15</v>
+        <v>93.37</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
@@ -2428,60 +2424,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.97</v>
+        <v>35.71</v>
       </c>
       <c r="D31" t="n">
-        <v>0.84</v>
+        <v>1.22</v>
       </c>
       <c r="E31" t="n">
-        <v>6.13</v>
+        <v>36.29</v>
       </c>
       <c r="F31" t="n">
-        <v>6.28</v>
+        <v>36.94</v>
       </c>
       <c r="G31" t="n">
-        <v>6.46</v>
+        <v>37.04</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.181</v>
+        <v>-0.504</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.128</v>
+        <v>-0.369</v>
       </c>
       <c r="J31" t="n">
-        <v>11.25</v>
+        <v>23.96</v>
       </c>
       <c r="K31" t="n">
-        <v>16.22</v>
+        <v>36.41</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>-0.95</v>
       </c>
       <c r="M31" t="n">
-        <v>9708.51</v>
+        <v>1530.36</v>
       </c>
       <c r="N31" t="n">
-        <v>14056.98</v>
+        <v>2618.46</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="P31" t="n">
-        <v>5.97</v>
+        <v>35.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>35.75</v>
       </c>
       <c r="R31" t="n">
-        <v>5.88</v>
+        <v>35.35</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
@@ -2492,60 +2488,60 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.88</v>
+        <v>15.61</v>
       </c>
       <c r="D32" t="n">
-        <v>0.65</v>
+        <v>6.84</v>
       </c>
       <c r="E32" t="n">
-        <v>95.95</v>
+        <v>14.11</v>
       </c>
       <c r="F32" t="n">
-        <v>96.61</v>
+        <v>13.38</v>
       </c>
       <c r="G32" t="n">
-        <v>95.8</v>
+        <v>11.81</v>
       </c>
       <c r="H32" t="n">
-        <v>0.198</v>
+        <v>1.105</v>
       </c>
       <c r="I32" t="n">
-        <v>0.467</v>
+        <v>0.72</v>
       </c>
       <c r="J32" t="n">
-        <v>35.13</v>
+        <v>80.45</v>
       </c>
       <c r="K32" t="n">
-        <v>56.1</v>
+        <v>77.34</v>
       </c>
       <c r="L32" t="n">
-        <v>-6.81</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>1014.2</v>
+        <v>14058.22</v>
       </c>
       <c r="N32" t="n">
-        <v>1144.22</v>
+        <v>5675.64</v>
       </c>
       <c r="O32" t="n">
-        <v>0.89</v>
+        <v>2.48</v>
       </c>
       <c r="P32" t="n">
-        <v>93.70999999999999</v>
+        <v>14.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>94.5</v>
+        <v>16</v>
       </c>
       <c r="R32" t="n">
-        <v>93.37</v>
+        <v>14.18</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
@@ -2556,60 +2552,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>35.71</v>
+        <v>17.43</v>
       </c>
       <c r="D33" t="n">
-        <v>1.22</v>
+        <v>3.38</v>
       </c>
       <c r="E33" t="n">
-        <v>36.29</v>
+        <v>17.97</v>
       </c>
       <c r="F33" t="n">
-        <v>36.94</v>
+        <v>18.92</v>
       </c>
       <c r="G33" t="n">
-        <v>37.04</v>
+        <v>19.84</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.504</v>
+        <v>-0.526</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.369</v>
+        <v>-0.092</v>
       </c>
       <c r="J33" t="n">
-        <v>23.96</v>
+        <v>11.21</v>
       </c>
       <c r="K33" t="n">
-        <v>36.41</v>
+        <v>13.28</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.95</v>
+        <v>7.07</v>
       </c>
       <c r="M33" t="n">
-        <v>1530.36</v>
+        <v>4451.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2618.46</v>
+        <v>6248.82</v>
       </c>
       <c r="O33" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="P33" t="n">
-        <v>35.61</v>
+        <v>17.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>35.75</v>
+        <v>17.44</v>
       </c>
       <c r="R33" t="n">
-        <v>35.35</v>
+        <v>16.83</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
@@ -2620,60 +2616,60 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15.61</v>
+        <v>31.39</v>
       </c>
       <c r="D34" t="n">
-        <v>6.84</v>
+        <v>1.03</v>
       </c>
       <c r="E34" t="n">
-        <v>14.11</v>
+        <v>32.47</v>
       </c>
       <c r="F34" t="n">
-        <v>13.38</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>11.81</v>
+        <v>35.16</v>
       </c>
       <c r="H34" t="n">
-        <v>1.105</v>
+        <v>-2.634</v>
       </c>
       <c r="I34" t="n">
-        <v>0.72</v>
+        <v>-2.531</v>
       </c>
       <c r="J34" t="n">
-        <v>80.45</v>
+        <v>13.1</v>
       </c>
       <c r="K34" t="n">
-        <v>77.34</v>
+        <v>21.1</v>
       </c>
       <c r="L34" t="n">
-        <v>86.65000000000001</v>
+        <v>-2.89</v>
       </c>
       <c r="M34" t="n">
-        <v>14058.22</v>
+        <v>2884.64</v>
       </c>
       <c r="N34" t="n">
-        <v>5675.64</v>
+        <v>4524.12</v>
       </c>
       <c r="O34" t="n">
-        <v>2.48</v>
+        <v>0.64</v>
       </c>
       <c r="P34" t="n">
-        <v>14.47</v>
+        <v>31.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>31.5</v>
       </c>
       <c r="R34" t="n">
-        <v>14.18</v>
+        <v>30.79</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
@@ -2684,60 +2680,60 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.43</v>
+        <v>48.48</v>
       </c>
       <c r="D35" t="n">
-        <v>3.38</v>
+        <v>-2.06</v>
       </c>
       <c r="E35" t="n">
-        <v>17.97</v>
+        <v>48.9</v>
       </c>
       <c r="F35" t="n">
-        <v>18.92</v>
+        <v>48.67</v>
       </c>
       <c r="G35" t="n">
-        <v>19.84</v>
+        <v>46.77</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.526</v>
+        <v>1.789</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.092</v>
+        <v>1.765</v>
       </c>
       <c r="J35" t="n">
-        <v>11.21</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>13.28</v>
+        <v>75.27</v>
       </c>
       <c r="L35" t="n">
-        <v>7.07</v>
+        <v>59.34</v>
       </c>
       <c r="M35" t="n">
-        <v>4451.95</v>
+        <v>4656.28</v>
       </c>
       <c r="N35" t="n">
-        <v>6248.82</v>
+        <v>4880.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="P35" t="n">
-        <v>17.08</v>
+        <v>48.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>17.44</v>
+        <v>49.29</v>
       </c>
       <c r="R35" t="n">
-        <v>16.83</v>
+        <v>47.9</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
@@ -2748,60 +2744,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>31.39</v>
+        <v>4.65</v>
       </c>
       <c r="D36" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="E36" t="n">
-        <v>32.47</v>
+        <v>4.88</v>
       </c>
       <c r="F36" t="n">
-        <v>34</v>
+        <v>5.26</v>
       </c>
       <c r="G36" t="n">
-        <v>35.16</v>
+        <v>5.68</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.634</v>
+        <v>-0.238</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.531</v>
+        <v>-0.066</v>
       </c>
       <c r="J36" t="n">
-        <v>13.1</v>
+        <v>8.19</v>
       </c>
       <c r="K36" t="n">
-        <v>21.1</v>
+        <v>10.62</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.89</v>
+        <v>3.33</v>
       </c>
       <c r="M36" t="n">
-        <v>2884.64</v>
+        <v>4000.37</v>
       </c>
       <c r="N36" t="n">
-        <v>4524.12</v>
+        <v>6039.77</v>
       </c>
       <c r="O36" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="P36" t="n">
-        <v>31.4</v>
+        <v>4.62</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.5</v>
+        <v>4.68</v>
       </c>
       <c r="R36" t="n">
-        <v>30.79</v>
+        <v>4.51</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
@@ -2812,191 +2808,63 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.48</v>
+        <v>34.8</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.06</v>
+        <v>0.2</v>
       </c>
       <c r="E37" t="n">
-        <v>48.9</v>
+        <v>34.88</v>
       </c>
       <c r="F37" t="n">
-        <v>48.67</v>
+        <v>36.56</v>
       </c>
       <c r="G37" t="n">
-        <v>46.77</v>
+        <v>35.51</v>
       </c>
       <c r="H37" t="n">
-        <v>1.789</v>
+        <v>0.762</v>
       </c>
       <c r="I37" t="n">
-        <v>1.765</v>
+        <v>1.192</v>
       </c>
       <c r="J37" t="n">
-        <v>69.95999999999999</v>
+        <v>19.05</v>
       </c>
       <c r="K37" t="n">
-        <v>75.27</v>
+        <v>28.45</v>
       </c>
       <c r="L37" t="n">
-        <v>59.34</v>
+        <v>0.25</v>
       </c>
       <c r="M37" t="n">
-        <v>4656.28</v>
+        <v>5399.86</v>
       </c>
       <c r="N37" t="n">
-        <v>4880.38</v>
+        <v>5858.36</v>
       </c>
       <c r="O37" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="P37" t="n">
-        <v>48.63</v>
+        <v>35.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>49.29</v>
+        <v>35.38</v>
       </c>
       <c r="R37" t="n">
-        <v>47.9</v>
+        <v>33.04</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>600963</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>岳阳林纸</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E38" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-0.238</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-0.066</v>
-      </c>
-      <c r="J38" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="K38" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="L38" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4000.37</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6039.77</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>601877</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>正泰电器</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="F39" t="n">
-        <v>36.56</v>
-      </c>
-      <c r="G39" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="J39" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="K39" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5399.86</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5858.36</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="P39" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="R39" t="n">
-        <v>33.04</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
